--- a/r5-TC-FHIR-AG-Messaging-R5-1-create-menu-structure-according-hl7-autria-reference-ig-framework/ValueSet-at-messaging-event-type-vs.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-1-create-menu-structure-according-hl7-autria-reference-ig-framework/ValueSet-at-messaging-event-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T07:37:21+00:00</t>
+    <t>2026-06-03T07:29:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Messaging-R5-1-create-menu-structure-according-hl7-autria-reference-ig-framework/ValueSet-at-messaging-event-type-vs.xlsx
+++ b/r5-TC-FHIR-AG-Messaging-R5-1-create-menu-structure-according-hl7-autria-reference-ig-framework/ValueSet-at-messaging-event-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:29:21+00:00</t>
+    <t>2026-06-03T07:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
